--- a/artfynd/A 53066-2024 artfynd.xlsx
+++ b/artfynd/A 53066-2024 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743096</v>
+        <v>122743089</v>
       </c>
       <c r="B5" t="n">
-        <v>78498</v>
+        <v>79844</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,21 +1049,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493956</v>
+        <v>493705</v>
       </c>
       <c r="R5" t="n">
-        <v>7122996</v>
+        <v>7123146</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743089</v>
+        <v>122743096</v>
       </c>
       <c r="B6" t="n">
-        <v>79844</v>
+        <v>78498</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493705</v>
+        <v>493956</v>
       </c>
       <c r="R6" t="n">
-        <v>7123146</v>
+        <v>7122996</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 53066-2024 artfynd.xlsx
+++ b/artfynd/A 53066-2024 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743089</v>
+        <v>122743096</v>
       </c>
       <c r="B5" t="n">
-        <v>79844</v>
+        <v>78502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,21 +1049,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493705</v>
+        <v>493956</v>
       </c>
       <c r="R5" t="n">
-        <v>7123146</v>
+        <v>7122996</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743096</v>
+        <v>122743103</v>
       </c>
       <c r="B6" t="n">
-        <v>78498</v>
+        <v>79848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493956</v>
+        <v>493923</v>
       </c>
       <c r="R6" t="n">
-        <v>7122996</v>
+        <v>7123124</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,7 +1248,7 @@
         <v>122743093</v>
       </c>
       <c r="B7" t="n">
-        <v>79844</v>
+        <v>79848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743095</v>
+        <v>122743094</v>
       </c>
       <c r="B8" t="n">
-        <v>79843</v>
+        <v>5489</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,34 +1367,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>101410</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493882</v>
+        <v>493861</v>
       </c>
       <c r="R8" t="n">
-        <v>7122997</v>
+        <v>7123027</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743103</v>
+        <v>122743095</v>
       </c>
       <c r="B9" t="n">
-        <v>79844</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,21 +1473,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493923</v>
+        <v>493882</v>
       </c>
       <c r="R9" t="n">
-        <v>7123124</v>
+        <v>7122997</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743094</v>
+        <v>122743089</v>
       </c>
       <c r="B10" t="n">
-        <v>5489</v>
+        <v>79848</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,34 +1579,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101410</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493861</v>
+        <v>493705</v>
       </c>
       <c r="R10" t="n">
-        <v>7123027</v>
+        <v>7123146</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1672,7 @@
         <v>122743092</v>
       </c>
       <c r="B11" t="n">
-        <v>90951</v>
+        <v>90955</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 53066-2024 artfynd.xlsx
+++ b/artfynd/A 53066-2024 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743096</v>
+        <v>122743095</v>
       </c>
       <c r="B5" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,21 +1049,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493956</v>
+        <v>493882</v>
       </c>
       <c r="R5" t="n">
-        <v>7122996</v>
+        <v>7122997</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743093</v>
+        <v>122743092</v>
       </c>
       <c r="B7" t="n">
-        <v>79848</v>
+        <v>90955</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,38 +1257,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493829</v>
+        <v>493781</v>
       </c>
       <c r="R7" t="n">
-        <v>7123036</v>
+        <v>7123147</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743094</v>
+        <v>122743089</v>
       </c>
       <c r="B8" t="n">
-        <v>5489</v>
+        <v>79848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,34 +1367,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101410</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493861</v>
+        <v>493705</v>
       </c>
       <c r="R8" t="n">
-        <v>7123027</v>
+        <v>7123146</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743095</v>
+        <v>122743093</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,34 +1473,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493882</v>
+        <v>493829</v>
       </c>
       <c r="R9" t="n">
-        <v>7122997</v>
+        <v>7123036</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743089</v>
+        <v>122743094</v>
       </c>
       <c r="B10" t="n">
-        <v>79848</v>
+        <v>5489</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,34 +1579,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>101410</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493705</v>
+        <v>493861</v>
       </c>
       <c r="R10" t="n">
-        <v>7123146</v>
+        <v>7123027</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743092</v>
+        <v>122743096</v>
       </c>
       <c r="B11" t="n">
-        <v>90955</v>
+        <v>78502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,25 +1681,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493781</v>
+        <v>493956</v>
       </c>
       <c r="R11" t="n">
-        <v>7123147</v>
+        <v>7122996</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 53066-2024 artfynd.xlsx
+++ b/artfynd/A 53066-2024 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743095</v>
+        <v>122743096</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,21 +1049,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493882</v>
+        <v>493956</v>
       </c>
       <c r="R5" t="n">
-        <v>7122997</v>
+        <v>7122996</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,7 +1139,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743103</v>
+        <v>122743093</v>
       </c>
       <c r="B6" t="n">
         <v>79848</v>
@@ -1175,14 +1175,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493923</v>
+        <v>493829</v>
       </c>
       <c r="R6" t="n">
-        <v>7123124</v>
+        <v>7123036</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743092</v>
+        <v>122743089</v>
       </c>
       <c r="B7" t="n">
-        <v>90955</v>
+        <v>79848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,25 +1257,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493781</v>
+        <v>493705</v>
       </c>
       <c r="R7" t="n">
-        <v>7123147</v>
+        <v>7123146</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743089</v>
+        <v>122743095</v>
       </c>
       <c r="B8" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493705</v>
+        <v>493882</v>
       </c>
       <c r="R8" t="n">
-        <v>7123146</v>
+        <v>7122997</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743093</v>
+        <v>122743094</v>
       </c>
       <c r="B9" t="n">
-        <v>79848</v>
+        <v>5489</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,21 +1473,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>101410</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493829</v>
+        <v>493861</v>
       </c>
       <c r="R9" t="n">
-        <v>7123036</v>
+        <v>7123027</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743094</v>
+        <v>122743092</v>
       </c>
       <c r="B10" t="n">
-        <v>5489</v>
+        <v>90955</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,38 +1575,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101410</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493861</v>
+        <v>493781</v>
       </c>
       <c r="R10" t="n">
-        <v>7123027</v>
+        <v>7123147</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743096</v>
+        <v>122743103</v>
       </c>
       <c r="B11" t="n">
-        <v>78502</v>
+        <v>79848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,21 +1685,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493956</v>
+        <v>493923</v>
       </c>
       <c r="R11" t="n">
-        <v>7122996</v>
+        <v>7123124</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 53066-2024 artfynd.xlsx
+++ b/artfynd/A 53066-2024 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743096</v>
+        <v>122743092</v>
       </c>
       <c r="B5" t="n">
-        <v>78502</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,25 +1045,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493956</v>
+        <v>493781</v>
       </c>
       <c r="R5" t="n">
-        <v>7122996</v>
+        <v>7123147</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743093</v>
+        <v>122743096</v>
       </c>
       <c r="B6" t="n">
-        <v>79848</v>
+        <v>78502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,34 +1155,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493829</v>
+        <v>493956</v>
       </c>
       <c r="R6" t="n">
-        <v>7123036</v>
+        <v>7122996</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743089</v>
+        <v>122743094</v>
       </c>
       <c r="B7" t="n">
-        <v>79848</v>
+        <v>5489</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>101410</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493705</v>
+        <v>493861</v>
       </c>
       <c r="R7" t="n">
-        <v>7123146</v>
+        <v>7123027</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743095</v>
+        <v>122743089</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493882</v>
+        <v>493705</v>
       </c>
       <c r="R8" t="n">
-        <v>7122997</v>
+        <v>7123146</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743094</v>
+        <v>122743103</v>
       </c>
       <c r="B9" t="n">
-        <v>5489</v>
+        <v>79848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,34 +1473,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101410</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493861</v>
+        <v>493923</v>
       </c>
       <c r="R9" t="n">
-        <v>7123027</v>
+        <v>7123124</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743092</v>
+        <v>122743095</v>
       </c>
       <c r="B10" t="n">
-        <v>90955</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493781</v>
+        <v>493882</v>
       </c>
       <c r="R10" t="n">
-        <v>7123147</v>
+        <v>7122997</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743103</v>
+        <v>122743093</v>
       </c>
       <c r="B11" t="n">
         <v>79848</v>
@@ -1705,14 +1705,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493923</v>
+        <v>493829</v>
       </c>
       <c r="R11" t="n">
-        <v>7123124</v>
+        <v>7123036</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 53066-2024 artfynd.xlsx
+++ b/artfynd/A 53066-2024 artfynd.xlsx
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743095</v>
+        <v>122743093</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,34 +1579,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493882</v>
+        <v>493829</v>
       </c>
       <c r="R10" t="n">
-        <v>7122997</v>
+        <v>7123036</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743093</v>
+        <v>122743095</v>
       </c>
       <c r="B11" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,34 +1685,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493829</v>
+        <v>493882</v>
       </c>
       <c r="R11" t="n">
-        <v>7123036</v>
+        <v>7122997</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 53066-2024 artfynd.xlsx
+++ b/artfynd/A 53066-2024 artfynd.xlsx
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743093</v>
+        <v>122743095</v>
       </c>
       <c r="B10" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,34 +1579,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493829</v>
+        <v>493882</v>
       </c>
       <c r="R10" t="n">
-        <v>7123036</v>
+        <v>7122997</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743095</v>
+        <v>122743093</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,34 +1685,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493882</v>
+        <v>493829</v>
       </c>
       <c r="R11" t="n">
-        <v>7122997</v>
+        <v>7123036</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 53066-2024 artfynd.xlsx
+++ b/artfynd/A 53066-2024 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743092</v>
+        <v>122743093</v>
       </c>
       <c r="B5" t="n">
-        <v>90955</v>
+        <v>79848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,38 +1045,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493781</v>
+        <v>493829</v>
       </c>
       <c r="R5" t="n">
-        <v>7123147</v>
+        <v>7123036</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743096</v>
+        <v>122743092</v>
       </c>
       <c r="B6" t="n">
-        <v>78502</v>
+        <v>90963</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,25 +1151,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493956</v>
+        <v>493781</v>
       </c>
       <c r="R6" t="n">
-        <v>7122996</v>
+        <v>7123147</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743094</v>
+        <v>122743089</v>
       </c>
       <c r="B7" t="n">
-        <v>5489</v>
+        <v>79848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101410</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493861</v>
+        <v>493705</v>
       </c>
       <c r="R7" t="n">
-        <v>7123027</v>
+        <v>7123146</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743089</v>
+        <v>122743096</v>
       </c>
       <c r="B8" t="n">
-        <v>79848</v>
+        <v>78502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493705</v>
+        <v>493956</v>
       </c>
       <c r="R8" t="n">
-        <v>7123146</v>
+        <v>7122996</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743103</v>
+        <v>122743094</v>
       </c>
       <c r="B9" t="n">
-        <v>79848</v>
+        <v>5489</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,34 +1473,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>101410</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493923</v>
+        <v>493861</v>
       </c>
       <c r="R9" t="n">
-        <v>7123124</v>
+        <v>7123027</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743093</v>
+        <v>122743103</v>
       </c>
       <c r="B11" t="n">
         <v>79848</v>
@@ -1705,14 +1705,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493829</v>
+        <v>493923</v>
       </c>
       <c r="R11" t="n">
-        <v>7123036</v>
+        <v>7123124</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 53066-2024 artfynd.xlsx
+++ b/artfynd/A 53066-2024 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743093</v>
+        <v>122743094</v>
       </c>
       <c r="B5" t="n">
-        <v>79848</v>
+        <v>5489</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,21 +1049,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>101410</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493829</v>
+        <v>493861</v>
       </c>
       <c r="R5" t="n">
-        <v>7123036</v>
+        <v>7123027</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743092</v>
+        <v>122743089</v>
       </c>
       <c r="B6" t="n">
-        <v>90963</v>
+        <v>79848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,25 +1151,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493781</v>
+        <v>493705</v>
       </c>
       <c r="R6" t="n">
-        <v>7123147</v>
+        <v>7123146</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743089</v>
+        <v>122743103</v>
       </c>
       <c r="B7" t="n">
         <v>79848</v>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493705</v>
+        <v>493923</v>
       </c>
       <c r="R7" t="n">
-        <v>7123146</v>
+        <v>7123124</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743096</v>
+        <v>122743095</v>
       </c>
       <c r="B8" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493956</v>
+        <v>493882</v>
       </c>
       <c r="R8" t="n">
-        <v>7122996</v>
+        <v>7122997</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743094</v>
+        <v>122743092</v>
       </c>
       <c r="B9" t="n">
-        <v>5489</v>
+        <v>90963</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,38 +1469,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101410</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493861</v>
+        <v>493781</v>
       </c>
       <c r="R9" t="n">
-        <v>7123027</v>
+        <v>7123147</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743095</v>
+        <v>122743096</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493882</v>
+        <v>493956</v>
       </c>
       <c r="R10" t="n">
-        <v>7122997</v>
+        <v>7122996</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743103</v>
+        <v>122743093</v>
       </c>
       <c r="B11" t="n">
         <v>79848</v>
@@ -1705,14 +1705,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493923</v>
+        <v>493829</v>
       </c>
       <c r="R11" t="n">
-        <v>7123124</v>
+        <v>7123036</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 53066-2024 artfynd.xlsx
+++ b/artfynd/A 53066-2024 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743094</v>
+        <v>122743095</v>
       </c>
       <c r="B5" t="n">
-        <v>5489</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,34 +1049,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101410</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493861</v>
+        <v>493882</v>
       </c>
       <c r="R5" t="n">
-        <v>7123027</v>
+        <v>7122997</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743089</v>
+        <v>122743096</v>
       </c>
       <c r="B6" t="n">
-        <v>79848</v>
+        <v>78502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493705</v>
+        <v>493956</v>
       </c>
       <c r="R6" t="n">
-        <v>7123146</v>
+        <v>7122996</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743103</v>
+        <v>122743094</v>
       </c>
       <c r="B7" t="n">
-        <v>79848</v>
+        <v>5489</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>101410</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493923</v>
+        <v>493861</v>
       </c>
       <c r="R7" t="n">
-        <v>7123124</v>
+        <v>7123027</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743095</v>
+        <v>122743092</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>90963</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,25 +1363,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493882</v>
+        <v>493781</v>
       </c>
       <c r="R8" t="n">
-        <v>7122997</v>
+        <v>7123147</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743092</v>
+        <v>122743089</v>
       </c>
       <c r="B9" t="n">
-        <v>90963</v>
+        <v>79848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,25 +1469,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493781</v>
+        <v>493705</v>
       </c>
       <c r="R9" t="n">
-        <v>7123147</v>
+        <v>7123146</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743096</v>
+        <v>122743093</v>
       </c>
       <c r="B10" t="n">
-        <v>78502</v>
+        <v>79848</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,34 +1579,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493956</v>
+        <v>493829</v>
       </c>
       <c r="R10" t="n">
-        <v>7122996</v>
+        <v>7123036</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743093</v>
+        <v>122743103</v>
       </c>
       <c r="B11" t="n">
         <v>79848</v>
@@ -1705,14 +1705,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493829</v>
+        <v>493923</v>
       </c>
       <c r="R11" t="n">
-        <v>7123036</v>
+        <v>7123124</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 53066-2024 artfynd.xlsx
+++ b/artfynd/A 53066-2024 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743095</v>
+        <v>122743103</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,21 +1049,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493882</v>
+        <v>493923</v>
       </c>
       <c r="R5" t="n">
-        <v>7122997</v>
+        <v>7123124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743096</v>
+        <v>122743089</v>
       </c>
       <c r="B6" t="n">
-        <v>78502</v>
+        <v>79848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493956</v>
+        <v>493705</v>
       </c>
       <c r="R6" t="n">
-        <v>7122996</v>
+        <v>7123146</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743094</v>
+        <v>122743095</v>
       </c>
       <c r="B7" t="n">
-        <v>5489</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101410</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493861</v>
+        <v>493882</v>
       </c>
       <c r="R7" t="n">
-        <v>7123027</v>
+        <v>7122997</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743092</v>
+        <v>122743093</v>
       </c>
       <c r="B8" t="n">
-        <v>90963</v>
+        <v>79848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,38 +1363,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493781</v>
+        <v>493829</v>
       </c>
       <c r="R8" t="n">
-        <v>7123147</v>
+        <v>7123036</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743089</v>
+        <v>122743096</v>
       </c>
       <c r="B9" t="n">
-        <v>79848</v>
+        <v>78502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,21 +1473,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493705</v>
+        <v>493956</v>
       </c>
       <c r="R9" t="n">
-        <v>7123146</v>
+        <v>7122996</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743093</v>
+        <v>122743094</v>
       </c>
       <c r="B10" t="n">
-        <v>79848</v>
+        <v>5489</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>101410</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493829</v>
+        <v>493861</v>
       </c>
       <c r="R10" t="n">
-        <v>7123036</v>
+        <v>7123027</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743103</v>
+        <v>122743092</v>
       </c>
       <c r="B11" t="n">
-        <v>79848</v>
+        <v>90963</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,25 +1681,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493923</v>
+        <v>493781</v>
       </c>
       <c r="R11" t="n">
-        <v>7123124</v>
+        <v>7123147</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 53066-2024 artfynd.xlsx
+++ b/artfynd/A 53066-2024 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743103</v>
+        <v>122743096</v>
       </c>
       <c r="B5" t="n">
-        <v>79848</v>
+        <v>78505</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,21 +1049,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493923</v>
+        <v>493956</v>
       </c>
       <c r="R5" t="n">
-        <v>7123124</v>
+        <v>7122996</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743089</v>
+        <v>122743093</v>
       </c>
       <c r="B6" t="n">
-        <v>79848</v>
+        <v>79851</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,14 +1175,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493705</v>
+        <v>493829</v>
       </c>
       <c r="R6" t="n">
-        <v>7123146</v>
+        <v>7123036</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743095</v>
+        <v>122743092</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>90966</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,25 +1257,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493882</v>
+        <v>493781</v>
       </c>
       <c r="R7" t="n">
-        <v>7122997</v>
+        <v>7123147</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743093</v>
+        <v>122743095</v>
       </c>
       <c r="B8" t="n">
-        <v>79848</v>
+        <v>79850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,34 +1367,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493829</v>
+        <v>493882</v>
       </c>
       <c r="R8" t="n">
-        <v>7123036</v>
+        <v>7122997</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743096</v>
+        <v>122743094</v>
       </c>
       <c r="B9" t="n">
-        <v>78502</v>
+        <v>5489</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,34 +1473,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>101410</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493956</v>
+        <v>493861</v>
       </c>
       <c r="R9" t="n">
-        <v>7122996</v>
+        <v>7123027</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743094</v>
+        <v>122743103</v>
       </c>
       <c r="B10" t="n">
-        <v>5489</v>
+        <v>79851</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,34 +1579,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101410</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493861</v>
+        <v>493923</v>
       </c>
       <c r="R10" t="n">
-        <v>7123027</v>
+        <v>7123124</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743092</v>
+        <v>122743089</v>
       </c>
       <c r="B11" t="n">
-        <v>90963</v>
+        <v>79851</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,25 +1681,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493781</v>
+        <v>493705</v>
       </c>
       <c r="R11" t="n">
-        <v>7123147</v>
+        <v>7123146</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 53066-2024 artfynd.xlsx
+++ b/artfynd/A 53066-2024 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743096</v>
+        <v>122743093</v>
       </c>
       <c r="B5" t="n">
-        <v>78505</v>
+        <v>79853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,34 +1049,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493956</v>
+        <v>493829</v>
       </c>
       <c r="R5" t="n">
-        <v>7122996</v>
+        <v>7123036</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743093</v>
+        <v>122743089</v>
       </c>
       <c r="B6" t="n">
-        <v>79851</v>
+        <v>79853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,14 +1175,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493829</v>
+        <v>493705</v>
       </c>
       <c r="R6" t="n">
-        <v>7123036</v>
+        <v>7123146</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,7 +1248,7 @@
         <v>122743092</v>
       </c>
       <c r="B7" t="n">
-        <v>90966</v>
+        <v>90968</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743095</v>
+        <v>122743096</v>
       </c>
       <c r="B8" t="n">
-        <v>79850</v>
+        <v>78507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493882</v>
+        <v>493956</v>
       </c>
       <c r="R8" t="n">
-        <v>7122997</v>
+        <v>7122996</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743094</v>
+        <v>122743103</v>
       </c>
       <c r="B9" t="n">
-        <v>5489</v>
+        <v>79853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,34 +1473,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101410</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493861</v>
+        <v>493923</v>
       </c>
       <c r="R9" t="n">
-        <v>7123027</v>
+        <v>7123124</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743103</v>
+        <v>122743094</v>
       </c>
       <c r="B10" t="n">
-        <v>79851</v>
+        <v>5489</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,34 +1579,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>101410</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493923</v>
+        <v>493861</v>
       </c>
       <c r="R10" t="n">
-        <v>7123124</v>
+        <v>7123027</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743089</v>
+        <v>122743095</v>
       </c>
       <c r="B11" t="n">
-        <v>79851</v>
+        <v>79852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,21 +1685,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493705</v>
+        <v>493882</v>
       </c>
       <c r="R11" t="n">
-        <v>7123146</v>
+        <v>7122997</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 53066-2024 artfynd.xlsx
+++ b/artfynd/A 53066-2024 artfynd.xlsx
@@ -1775,7 +1775,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467415</v>
+        <v>124467414</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493506</v>
+        <v>493786</v>
       </c>
       <c r="R12" t="n">
-        <v>7123062</v>
+        <v>7123090</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467414</v>
+        <v>124467415</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493786</v>
+        <v>493506</v>
       </c>
       <c r="R13" t="n">
-        <v>7123090</v>
+        <v>7123062</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 53066-2024 artfynd.xlsx
+++ b/artfynd/A 53066-2024 artfynd.xlsx
@@ -1775,7 +1775,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467414</v>
+        <v>124467415</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493786</v>
+        <v>493506</v>
       </c>
       <c r="R12" t="n">
-        <v>7123090</v>
+        <v>7123062</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467415</v>
+        <v>124467414</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493506</v>
+        <v>493786</v>
       </c>
       <c r="R13" t="n">
-        <v>7123062</v>
+        <v>7123090</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 53066-2024 artfynd.xlsx
+++ b/artfynd/A 53066-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1971353</v>
+        <v>122743092</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvisselnvattnet S, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493598.4025894054</v>
+        <v>493781</v>
       </c>
       <c r="R2" t="n">
-        <v>7123291.334908877</v>
+        <v>7123147</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-06-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-06-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>avverkningsanmält och avverkat för en skogsbilväg av markägaren Holmen Skog AB</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,40 +756,30 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>hyggeskant</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Steget Före</t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89591561</v>
+        <v>122743089</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,34 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvisselnvattnet, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493757.8021604316</v>
+        <v>493705</v>
       </c>
       <c r="R3" t="n">
-        <v>7123261.854684877</v>
+        <v>7123146</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,31 +861,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89591510</v>
+        <v>122743093</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,34 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvisselnvattnet, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493757.8021604316</v>
+        <v>493829</v>
       </c>
       <c r="R4" t="n">
-        <v>7123261.854684877</v>
+        <v>7123036</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,22 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,26 +962,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122743093</v>
+        <v>122743103</v>
       </c>
       <c r="B5" t="n">
-        <v>80438</v>
+        <v>80489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,14 +1009,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493829</v>
+        <v>493923</v>
       </c>
       <c r="R5" t="n">
-        <v>7123036</v>
+        <v>7123124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122743089</v>
+        <v>89591510</v>
       </c>
       <c r="B6" t="n">
-        <v>80438</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,34 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Kvisselnvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493705</v>
+        <v>493758</v>
       </c>
       <c r="R6" t="n">
-        <v>7123146</v>
+        <v>7123262</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,48 +1164,48 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122743092</v>
+        <v>122743096</v>
       </c>
       <c r="B7" t="n">
-        <v>91928</v>
+        <v>79130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493781</v>
+        <v>493956</v>
       </c>
       <c r="R7" t="n">
-        <v>7123147</v>
+        <v>7122996</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122743096</v>
+        <v>89591561</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,34 +1292,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Kvisselnvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493956</v>
+        <v>493758</v>
       </c>
       <c r="R8" t="n">
-        <v>7122996</v>
+        <v>7123262</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,12 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,26 +1366,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122743103</v>
+        <v>1971353</v>
       </c>
       <c r="B9" t="n">
-        <v>80438</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1448,37 +1393,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Kvisselnvattnet S, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493923</v>
+        <v>493598</v>
       </c>
       <c r="R9" t="n">
-        <v>7123124</v>
+        <v>7123291</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1502,12 +1447,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2011-06-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2011-06-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>avverkningsanmält och avverkat för en skogsbilväg av markägaren Holmen Skog AB</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1518,30 +1468,35 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>hyggeskant</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+          <t>Steget Före</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122743094</v>
+        <v>122743095</v>
       </c>
       <c r="B10" t="n">
-        <v>5495</v>
+        <v>80488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,34 +1504,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101410</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stormyrberget SV, Jmt</t>
+          <t>Nedre Rosinedal SV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493861</v>
+        <v>493882</v>
       </c>
       <c r="R10" t="n">
-        <v>7123027</v>
+        <v>7122997</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,45 +1594,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122743095</v>
+        <v>89591541</v>
       </c>
       <c r="B11" t="n">
-        <v>80437</v>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedre Rosinedal SV, Jmt</t>
+          <t>Kvisselnvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493882</v>
+        <v>493995</v>
       </c>
       <c r="R11" t="n">
-        <v>7122997</v>
+        <v>7122950</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,12 +1659,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,66 +1679,61 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467414</v>
+        <v>122743094</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5497</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>101410</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kvisselnvattnet, Jmt</t>
+          <t>Stormyrberget SV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493786</v>
+        <v>493861</v>
       </c>
       <c r="R12" t="n">
-        <v>7123090</v>
+        <v>7123027</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,17 +1760,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1835,27 +1780,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467415</v>
+        <v>124467414</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493506</v>
+        <v>493786</v>
       </c>
       <c r="R13" t="n">
-        <v>7123062</v>
+        <v>7123090</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,6 +1895,108 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124467415</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kvisselnvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>493506</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7123062</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
